--- a/microcontroller_options.xlsx
+++ b/microcontroller_options.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phil\Documents\code\dmx_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35511FDC-9E1E-43C6-8761-61B51FDF2D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0265CC-97CB-41A9-9FD2-D43BE83F599D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{24F07B61-6DBE-4702-A4DD-8EAE7296E2EB}"/>
+    <workbookView xWindow="1440" yWindow="1420" windowWidth="25630" windowHeight="19110" activeTab="3" xr2:uid="{24F07B61-6DBE-4702-A4DD-8EAE7296E2EB}"/>
   </bookViews>
   <sheets>
     <sheet name="F746ZG" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="337">
   <si>
     <t>CN8</t>
   </si>
@@ -1047,13 +1047,16 @@
   </si>
   <si>
     <t>SPI6</t>
+  </si>
+  <si>
+    <t>USART 1 or 6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1089,6 +1092,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1097,7 +1114,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1108,6 +1125,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -1251,11 +1278,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1294,15 +1323,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="1" builtinId="10"/>
+    <cellStyle name="Note" xfId="3" builtinId="10"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -4325,13 +4358,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91741B41-C6F0-46ED-856A-DE009374055E}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="26.453125" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>301</v>
       </c>
@@ -4341,8 +4374,9 @@
       <c r="C1" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="17"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>301</v>
       </c>
@@ -4353,7 +4387,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>301</v>
       </c>
@@ -4363,8 +4397,9 @@
       <c r="C3" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D3" s="18"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>301</v>
       </c>
@@ -4375,7 +4410,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>302</v>
       </c>
@@ -4386,7 +4421,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>302</v>
       </c>
@@ -4397,7 +4432,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>302</v>
       </c>
@@ -4408,7 +4443,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>302</v>
       </c>
@@ -4419,7 +4454,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>303</v>
       </c>
@@ -4430,7 +4465,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>303</v>
       </c>
@@ -4441,7 +4476,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>303</v>
       </c>
@@ -4452,7 +4487,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>303</v>
       </c>
@@ -4463,7 +4498,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>314</v>
       </c>
@@ -4474,7 +4509,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>314</v>
       </c>
@@ -4485,7 +4520,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>314</v>
       </c>
@@ -4496,7 +4531,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>314</v>
       </c>
@@ -4507,7 +4542,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>315</v>
       </c>
@@ -4517,8 +4552,11 @@
       <c r="C19" s="15" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19" s="17" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>315</v>
       </c>
@@ -4529,7 +4567,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
         <v>315</v>
       </c>
@@ -4539,8 +4577,11 @@
       <c r="C21" s="15" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21" s="18" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>319</v>
       </c>
@@ -4551,7 +4592,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>319</v>
       </c>
@@ -4562,7 +4603,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>320</v>
       </c>
@@ -4573,7 +4614,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>320</v>
       </c>
@@ -4584,7 +4625,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>320</v>
       </c>
@@ -4595,7 +4636,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>321</v>
       </c>
@@ -4606,7 +4647,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>321</v>
       </c>
@@ -4617,7 +4658,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>322</v>
       </c>
@@ -4628,7 +4669,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>322</v>
       </c>
@@ -4639,7 +4680,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>323</v>
       </c>
@@ -4650,7 +4691,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>323</v>
       </c>
@@ -4661,7 +4702,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>324</v>
       </c>
@@ -4672,7 +4713,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>324</v>
       </c>
@@ -4683,7 +4724,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
         <v>267</v>
       </c>
@@ -4694,7 +4735,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
         <v>267</v>
       </c>
@@ -4704,8 +4745,11 @@
       <c r="C36" s="15" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D36" s="17" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
         <v>267</v>
       </c>
@@ -4716,7 +4760,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="15" t="s">
         <v>267</v>
       </c>
@@ -4726,8 +4770,11 @@
       <c r="C38" s="15" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D38" s="18" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="15" t="s">
         <v>329</v>
       </c>
@@ -4738,7 +4785,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="15" t="s">
         <v>329</v>
       </c>
@@ -4749,7 +4796,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="15" t="s">
         <v>329</v>
       </c>
@@ -4760,7 +4807,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="15" t="s">
         <v>329</v>
       </c>
@@ -4771,7 +4818,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="16" t="s">
         <v>330</v>
       </c>
@@ -4782,7 +4829,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="16" t="s">
         <v>330</v>
       </c>
@@ -4793,7 +4840,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="16" t="s">
         <v>330</v>
       </c>
@@ -4804,7 +4851,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="16" t="s">
         <v>330</v>
       </c>
@@ -4815,7 +4862,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
         <v>331</v>
       </c>
@@ -4826,7 +4873,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="16" t="s">
         <v>331</v>
       </c>
@@ -4837,7 +4884,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="16" t="s">
         <v>331</v>
       </c>
@@ -4848,7 +4895,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="16" t="s">
         <v>331</v>
       </c>
@@ -4859,7 +4906,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="15" t="s">
         <v>333</v>
       </c>
@@ -4869,8 +4916,9 @@
       <c r="C53" s="15" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D53" s="17"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="15" t="s">
         <v>333</v>
       </c>
@@ -4881,7 +4929,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="15" t="s">
         <v>333</v>
       </c>
@@ -4891,8 +4939,9 @@
       <c r="C55" s="15" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D55" s="18"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="15" t="s">
         <v>333</v>
       </c>
@@ -4903,7 +4952,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="15" t="s">
         <v>333</v>
       </c>
@@ -4914,7 +4963,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="15" t="s">
         <v>334</v>
       </c>
@@ -4924,8 +4973,9 @@
       <c r="C58" s="15" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D58" s="17"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="15" t="s">
         <v>334</v>
       </c>
@@ -4936,7 +4986,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="15" t="s">
         <v>334</v>
       </c>
@@ -4946,8 +4996,9 @@
       <c r="C60" s="15" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D60" s="18"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="15" t="s">
         <v>334</v>
       </c>
@@ -4958,7 +5009,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="15" t="s">
         <v>335</v>
       </c>
@@ -4968,8 +5019,9 @@
       <c r="C62" s="15" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D62" s="17"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="15" t="s">
         <v>335</v>
       </c>
@@ -4979,6 +5031,7 @@
       <c r="C63" s="15" t="s">
         <v>317</v>
       </c>
+      <c r="D63" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/microcontroller_options.xlsx
+++ b/microcontroller_options.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phil\Documents\code\dmx_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0265CC-97CB-41A9-9FD2-D43BE83F599D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF46C2C-1353-4927-921C-6908B32EB943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1420" windowWidth="25630" windowHeight="19110" activeTab="3" xr2:uid="{24F07B61-6DBE-4702-A4DD-8EAE7296E2EB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{24F07B61-6DBE-4702-A4DD-8EAE7296E2EB}"/>
   </bookViews>
   <sheets>
     <sheet name="F746ZG" sheetId="1" r:id="rId1"/>
@@ -1284,7 +1284,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1305,15 +1305,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1327,9 +1318,26 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -2900,48 +2908,48 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="9">
         <v>21</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F39" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="9">
         <v>19</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3153,25 +3161,25 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="9">
         <v>15</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F50" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="G50" s="13" t="s">
+      <c r="G50" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3199,25 +3207,25 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B52" s="12">
+      <c r="B52" s="9">
         <v>13</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3797,25 +3805,25 @@
       </c>
     </row>
     <row r="78" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B78" s="14">
+      <c r="B78" s="11">
         <v>12</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D78" s="14" t="s">
+      <c r="D78" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E78" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="F78" s="14" t="s">
+      <c r="F78" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="G78" s="14" t="s">
+      <c r="G78" s="11" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3843,25 +3851,25 @@
       </c>
     </row>
     <row r="80" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B80" s="14">
+      <c r="B80" s="11">
         <v>10</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D80" s="14" t="s">
+      <c r="D80" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="F80" s="14" t="s">
+      <c r="F80" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="G80" s="14" t="s">
+      <c r="G80" s="11" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4119,25 +4127,25 @@
       </c>
     </row>
     <row r="92" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="B92" s="12">
+      <c r="B92" s="9">
         <v>31</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="E92" s="12" t="s">
+      <c r="E92" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="F92" s="12" t="s">
+      <c r="F92" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="G92" s="13" t="s">
+      <c r="G92" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4234,117 +4242,117 @@
       </c>
     </row>
     <row r="97" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B97" s="12">
+      <c r="B97" s="9">
         <v>6</v>
       </c>
-      <c r="C97" s="12" t="s">
+      <c r="C97" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="D97" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E97" s="12" t="s">
+      <c r="E97" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F97" s="12" t="s">
+      <c r="F97" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G97" s="13" t="s">
+      <c r="G97" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A98" s="11" t="s">
+      <c r="A98" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B98" s="12">
+      <c r="B98" s="9">
         <v>4</v>
       </c>
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D98" s="12" t="s">
+      <c r="D98" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E98" s="12" t="s">
+      <c r="E98" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F98" s="12" t="s">
+      <c r="F98" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G98" s="13" t="s">
+      <c r="G98" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A99" s="11" t="s">
+      <c r="A99" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B99" s="12">
+      <c r="B99" s="9">
         <v>2</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E99" s="12" t="s">
+      <c r="E99" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F99" s="12" t="s">
+      <c r="F99" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G99" s="13" t="s">
+      <c r="G99" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B100" s="16">
         <v>14</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D100" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E100" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="F100" s="2" t="s">
+      <c r="F100" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B101" s="9">
+      <c r="B101" s="19">
         <v>16</v>
       </c>
-      <c r="C101" s="9" t="s">
+      <c r="C101" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="D101" s="9" t="s">
+      <c r="D101" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="E101" s="9" t="s">
+      <c r="E101" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="F101" s="9" t="s">
+      <c r="F101" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="G101" s="10" t="s">
+      <c r="G101" s="20" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4374,7 +4382,7 @@
       <c r="C1" t="s">
         <v>305</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -4397,7 +4405,7 @@
       <c r="C3" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="18"/>
+      <c r="D3" s="14"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -4543,41 +4551,41 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="13" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="12" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="14" t="s">
         <v>336</v>
       </c>
     </row>
@@ -4725,101 +4733,101 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="12" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="13" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="12" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="14" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="12" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="12" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="12" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="12" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="16" t="s">
+      <c r="A45" t="s">
         <v>330</v>
       </c>
       <c r="B45" t="s">
@@ -4830,7 +4838,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="16" t="s">
+      <c r="A46" t="s">
         <v>330</v>
       </c>
       <c r="B46" t="s">
@@ -4841,7 +4849,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="16" t="s">
+      <c r="A47" t="s">
         <v>330</v>
       </c>
       <c r="B47" t="s">
@@ -4852,7 +4860,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="16" t="s">
+      <c r="A48" t="s">
         <v>330</v>
       </c>
       <c r="B48" t="s">
@@ -4863,7 +4871,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="16" t="s">
+      <c r="A49" t="s">
         <v>331</v>
       </c>
       <c r="B49" t="s">
@@ -4874,7 +4882,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="16" t="s">
+      <c r="A50" t="s">
         <v>331</v>
       </c>
       <c r="B50" t="s">
@@ -4885,7 +4893,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="16" t="s">
+      <c r="A51" t="s">
         <v>331</v>
       </c>
       <c r="B51" t="s">
@@ -4896,7 +4904,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="16" t="s">
+      <c r="A52" t="s">
         <v>331</v>
       </c>
       <c r="B52" t="s">
@@ -4907,131 +4915,131 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="D53" s="17"/>
+      <c r="D53" s="13"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="12" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="D55" s="18"/>
+      <c r="D55" s="14"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="12" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="12" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="D58" s="17"/>
+      <c r="D58" s="13"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="12" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="D60" s="18"/>
+      <c r="D60" s="14"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C61" s="12" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="C62" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="D62" s="17"/>
+      <c r="D62" s="13"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="D63" s="18"/>
+      <c r="D63" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
